--- a/data/trans_orig/P1803_2016_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1803_2016_2023-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32839</t>
+          <t>32050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>23704</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44689</t>
+          <t>46307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42354</t>
+          <t>42590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71069</t>
+          <t>72046</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260922</t>
+          <t>261711</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279374</t>
+          <t>279994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>244014</t>
+          <t>242396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>266352</t>
+          <t>264999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>511395</t>
+          <t>510418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>540110</t>
+          <t>539874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19396</t>
+          <t>18811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7710</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>24311</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15807</t>
+          <t>16350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37413</t>
+          <t>36372</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483179</t>
+          <t>483764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>497316</t>
+          <t>497440</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499639</t>
+          <t>498773</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>515469</t>
+          <t>515374</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>988246</t>
+          <t>989287</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1009852</t>
+          <t>1009309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12576</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14079</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305989</t>
+          <t>307780</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316741</t>
+          <t>316769</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322230</t>
+          <t>322345</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333149</t>
+          <t>333235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>633975</t>
+          <t>632939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>648200</t>
+          <t>648205</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>18581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40364</t>
+          <t>40565</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39389</t>
+          <t>39079</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41836</t>
+          <t>40193</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71575</t>
+          <t>70144</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>329600</t>
+          <t>329399</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351014</t>
+          <t>351383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347894</t>
+          <t>348204</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>370324</t>
+          <t>369663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>685672</t>
+          <t>687103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>715411</t>
+          <t>717054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15926</t>
+          <t>16245</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22053</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201335</t>
+          <t>201810</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209573</t>
+          <t>209579</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202661</t>
+          <t>202342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214653</t>
+          <t>214662</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407755</t>
+          <t>408824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>422547</t>
+          <t>422689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29835</t>
+          <t>29080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22378</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45617</t>
+          <t>45036</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233288</t>
+          <t>234043</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250523</t>
+          <t>251061</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>252604</t>
+          <t>252890</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266030</t>
+          <t>267037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>490621</t>
+          <t>491202</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513860</t>
+          <t>513898</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23091</t>
+          <t>23219</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47790</t>
+          <t>47311</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27970</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54196</t>
+          <t>54155</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55938</t>
+          <t>55745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90265</t>
+          <t>92768</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>608768</t>
+          <t>609247</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>633467</t>
+          <t>633339</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>637098</t>
+          <t>637139</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>663324</t>
+          <t>663224</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1257587</t>
+          <t>1255084</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1291914</t>
+          <t>1292107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42908</t>
+          <t>43333</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40713</t>
+          <t>41004</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72006</t>
+          <t>69936</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68701</t>
+          <t>69115</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>105388</t>
+          <t>106905</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>735675</t>
+          <t>735250</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>757950</t>
+          <t>757693</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>754161</t>
+          <t>756231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>785454</t>
+          <t>785163</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1499362</t>
+          <t>1497845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1536049</t>
+          <t>1535635</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>130818</t>
+          <t>132226</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>180874</t>
+          <t>181067</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>166982</t>
+          <t>169707</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>225840</t>
+          <t>223109</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>312431</t>
+          <t>315049</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>390129</t>
+          <t>391061</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3213476</t>
+          <t>3213283</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3263532</t>
+          <t>3262124</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3318702</t>
+          <t>3321433</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3377560</t>
+          <t>3374835</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6548763</t>
+          <t>6547831</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6626461</t>
+          <t>6623843</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -4049,32 +4049,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44551</t>
+          <t>43214</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32450</t>
+          <t>32892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59015</t>
+          <t>55867</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>61844</t>
+          <t>62455</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51659</t>
+          <t>52332</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74792</t>
+          <t>75905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4119,32 +4119,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>106395</t>
+          <t>105668</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90090</t>
+          <t>89298</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125051</t>
+          <t>123882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -4162,32 +4162,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>266892</t>
+          <t>275631</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252428</t>
+          <t>262978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278993</t>
+          <t>285953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>227791</t>
+          <t>253606</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214843</t>
+          <t>240156</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>237976</t>
+          <t>263729</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4232,32 +4232,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>494682</t>
+          <t>529238</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>476026</t>
+          <t>511024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>510987</t>
+          <t>545608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -4275,17 +4275,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30831</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17913</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47621</t>
+          <t>47240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>44828</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32682</t>
+          <t>34080</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55926</t>
+          <t>60133</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>74024</t>
+          <t>75015</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56602</t>
+          <t>58494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95682</t>
+          <t>98417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>487559</t>
+          <t>500459</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>470769</t>
+          <t>483407</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500477</t>
+          <t>511576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>470532</t>
+          <t>500385</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>457799</t>
+          <t>485080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>481043</t>
+          <t>511133</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>958091</t>
+          <t>1000845</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936433</t>
+          <t>977443</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>975513</t>
+          <t>1017366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4688,17 +4688,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032115</t>
+          <t>1075860</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032115</t>
+          <t>1075860</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032115</t>
+          <t>1075860</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>32744</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23912</t>
+          <t>23610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44341</t>
+          <t>45405</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42408</t>
+          <t>42508</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32859</t>
+          <t>32655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53530</t>
+          <t>53817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4805,32 +4805,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>75792</t>
+          <t>75252</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61907</t>
+          <t>61045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92247</t>
+          <t>90268</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>282667</t>
+          <t>283249</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271709</t>
+          <t>270588</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>292138</t>
+          <t>292383</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>306217</t>
+          <t>313334</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>295095</t>
+          <t>302025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315766</t>
+          <t>323187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>588883</t>
+          <t>596584</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>572428</t>
+          <t>581568</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>602768</t>
+          <t>610791</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -4961,17 +4961,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664675</t>
+          <t>671836</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664675</t>
+          <t>671836</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664675</t>
+          <t>671836</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34221</t>
+          <t>36289</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>25058</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48484</t>
+          <t>52663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43413</t>
+          <t>47932</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26308</t>
+          <t>38045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59997</t>
+          <t>60980</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5148,32 +5148,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>77634</t>
+          <t>84221</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53215</t>
+          <t>67883</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96781</t>
+          <t>104245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>278336</t>
+          <t>336856</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>264073</t>
+          <t>320482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>289361</t>
+          <t>348087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>432305</t>
+          <t>374029</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>415721</t>
+          <t>360981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>449410</t>
+          <t>383916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>710640</t>
+          <t>710886</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691493</t>
+          <t>690862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>735059</t>
+          <t>727224</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -5304,17 +5304,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5421,32 +5421,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5456,22 +5456,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5491,32 +5491,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>22347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -5534,32 +5534,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>171394</t>
+          <t>198024</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164515</t>
+          <t>190713</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175149</t>
+          <t>202293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5569,27 +5569,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>220683</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197540</t>
+          <t>215150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205287</t>
+          <t>223559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5604,32 +5604,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>373901</t>
+          <t>418706</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>365066</t>
+          <t>410532</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379078</t>
+          <t>423964</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5647,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5717,17 +5717,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5764,32 +5764,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>22594</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>15212</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33612</t>
+          <t>32505</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34748</t>
+          <t>35829</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27215</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44014</t>
+          <t>45359</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5834,32 +5834,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>57940</t>
+          <t>58423</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>46398</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70102</t>
+          <t>70083</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -5877,32 +5877,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>246444</t>
+          <t>248113</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236024</t>
+          <t>238202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254260</t>
+          <t>255495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5912,32 +5912,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>222308</t>
+          <t>227921</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213042</t>
+          <t>218391</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>229841</t>
+          <t>236074</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5947,32 +5947,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>468752</t>
+          <t>476034</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>456590</t>
+          <t>464374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>479613</t>
+          <t>488059</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -5990,17 +5990,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6025,17 +6025,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6107,32 +6107,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>80839</t>
+          <t>90905</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61764</t>
+          <t>72537</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>102192</t>
+          <t>114562</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6142,32 +6142,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>97396</t>
+          <t>110666</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45655</t>
+          <t>93933</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>135414</t>
+          <t>128789</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>178234</t>
+          <t>201570</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111010</t>
+          <t>176805</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>218226</t>
+          <t>231251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -6220,32 +6220,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>543440</t>
+          <t>628782</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>522087</t>
+          <t>605125</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>562515</t>
+          <t>647150</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6255,32 +6255,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>751869</t>
+          <t>661391</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>713851</t>
+          <t>643268</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>803610</t>
+          <t>678124</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1295310</t>
+          <t>1290174</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1255318</t>
+          <t>1260493</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1362534</t>
+          <t>1314939</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -6333,17 +6333,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6403,17 +6403,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6450,32 +6450,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>260140</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18046</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>632568</t>
+          <t>30652</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6485,32 +6485,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>13910</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25144</t>
+          <t>28616</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6520,32 +6520,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>276882</t>
+          <t>38480</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33448</t>
+          <t>27130</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>791727</t>
+          <t>51344</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -6563,32 +6563,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>668580</t>
+          <t>779648</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>296152</t>
+          <t>767420</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>910674</t>
+          <t>786786</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6598,32 +6598,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>700990</t>
+          <t>811275</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>692587</t>
+          <t>802715</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>706309</t>
+          <t>817421</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6633,32 +6633,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1369570</t>
+          <t>1590923</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>854725</t>
+          <t>1578059</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1613004</t>
+          <t>1602273</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -6676,17 +6676,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6746,17 +6746,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>514507</t>
+          <t>281996</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>278006</t>
+          <t>249779</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1172526</t>
+          <t>322394</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>345891</t>
+          <t>370807</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>283016</t>
+          <t>337119</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>387944</t>
+          <t>401514</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6863,32 +6863,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>860399</t>
+          <t>652803</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>619385</t>
+          <t>610512</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1663521</t>
+          <t>704185</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -6906,32 +6906,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2945310</t>
+          <t>3250766</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2287291</t>
+          <t>3210368</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3181811</t>
+          <t>3282983</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3314519</t>
+          <t>3362624</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3272466</t>
+          <t>3331917</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3377394</t>
+          <t>3396312</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6976,32 +6976,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6259828</t>
+          <t>6613390</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5456706</t>
+          <t>6562008</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6500842</t>
+          <t>6655681</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -7019,17 +7019,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3660410</t>
+          <t>3733431</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3660410</t>
+          <t>3733431</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3660410</t>
+          <t>3733431</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7089,17 +7089,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7120227</t>
+          <t>7266193</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7120227</t>
+          <t>7266193</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7120227</t>
+          <t>7266193</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
